--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/85.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/85.xlsx
@@ -426,13 +426,13 @@
         <v>-11.46362227094832</v>
       </c>
       <c r="E2">
-        <v>-10.67385532190904</v>
+        <v>-7.039456051469073</v>
       </c>
       <c r="F2">
-        <v>-3.326519030141831</v>
+        <v>-3.236146631598613</v>
       </c>
       <c r="G2">
-        <v>-6.015738000957906</v>
+        <v>-5.474090352032571</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.04983521279129</v>
       </c>
       <c r="E3">
-        <v>-10.64353265995368</v>
+        <v>-8.876476817420631</v>
       </c>
       <c r="F3">
-        <v>-3.142090483215146</v>
+        <v>-2.952301570824946</v>
       </c>
       <c r="G3">
-        <v>-6.065350070936711</v>
+        <v>-5.173343427558546</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.59932960705994</v>
       </c>
       <c r="E4">
-        <v>-11.98185522581054</v>
+        <v>-8.458217901124181</v>
       </c>
       <c r="F4">
-        <v>-3.134122417167618</v>
+        <v>-2.550252623508803</v>
       </c>
       <c r="G4">
-        <v>-6.031238491604723</v>
+        <v>-5.377054786855112</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.14620220801936</v>
       </c>
       <c r="E5">
-        <v>-13.12500961888482</v>
+        <v>-9.612589324315461</v>
       </c>
       <c r="F5">
-        <v>-3.094240668559836</v>
+        <v>-2.441073799819828</v>
       </c>
       <c r="G5">
-        <v>-5.406739998303408</v>
+        <v>-4.971620488527003</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.652831262736353</v>
       </c>
       <c r="E6">
-        <v>-12.56379583511423</v>
+        <v>-9.979056083386185</v>
       </c>
       <c r="F6">
-        <v>-2.87178011743582</v>
+        <v>-3.02535115024082</v>
       </c>
       <c r="G6">
-        <v>-5.377231972819322</v>
+        <v>-4.90398466852217</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.11016823107977</v>
       </c>
       <c r="E7">
-        <v>-13.65121829857612</v>
+        <v>-11.40583333203487</v>
       </c>
       <c r="F7">
-        <v>-2.868238846788852</v>
+        <v>-2.389701766967814</v>
       </c>
       <c r="G7">
-        <v>-5.266874648110518</v>
+        <v>-5.228320294787042</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.498920781653922</v>
       </c>
       <c r="E8">
-        <v>-13.42848530450885</v>
+        <v>-11.32776244014263</v>
       </c>
       <c r="F8">
-        <v>-2.915297570574489</v>
+        <v>-2.407423030815904</v>
       </c>
       <c r="G8">
-        <v>-5.247663095879969</v>
+        <v>-5.095053481150195</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.827260770721645</v>
       </c>
       <c r="E9">
-        <v>-14.67709880027376</v>
+        <v>-13.69344179022364</v>
       </c>
       <c r="F9">
-        <v>-2.933481891800744</v>
+        <v>-2.913769232716324</v>
       </c>
       <c r="G9">
-        <v>-4.955693439077459</v>
+        <v>-4.553320520464313</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.105207624303506</v>
       </c>
       <c r="E10">
-        <v>-14.58613081440768</v>
+        <v>-13.09648476111051</v>
       </c>
       <c r="F10">
-        <v>-2.738400540074057</v>
+        <v>-2.361260600560096</v>
       </c>
       <c r="G10">
-        <v>-4.121895666163844</v>
+        <v>-3.232320407961227</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.348515179706048</v>
       </c>
       <c r="E11">
-        <v>-15.8026329009842</v>
+        <v>-14.11039650600588</v>
       </c>
       <c r="F11">
-        <v>-2.940252966951227</v>
+        <v>-2.247172871642131</v>
       </c>
       <c r="G11">
-        <v>-4.026635241850045</v>
+        <v>-3.770270120189069</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.579759364650999</v>
       </c>
       <c r="E12">
-        <v>-15.86159816103807</v>
+        <v>-13.63374291738052</v>
       </c>
       <c r="F12">
-        <v>-2.572298793566909</v>
+        <v>-1.695372493615296</v>
       </c>
       <c r="G12">
-        <v>-2.688366060279601</v>
+        <v>-2.923993861684886</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.812433171303477</v>
       </c>
       <c r="E13">
-        <v>-17.05473785020902</v>
+        <v>-14.85079747778597</v>
       </c>
       <c r="F13">
-        <v>-2.687857702992245</v>
+        <v>-1.923539667777198</v>
       </c>
       <c r="G13">
-        <v>-2.17008727130063</v>
+        <v>-2.004595580728476</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.076227040217994</v>
       </c>
       <c r="E14">
-        <v>-17.75782419616591</v>
+        <v>-15.461865231907</v>
       </c>
       <c r="F14">
-        <v>-2.868398721697592</v>
+        <v>-1.959258870185912</v>
       </c>
       <c r="G14">
-        <v>-2.327343095758577</v>
+        <v>-1.382338161752261</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.394702808685673</v>
       </c>
       <c r="E15">
-        <v>-18.60833954191652</v>
+        <v>-16.07536930504416</v>
       </c>
       <c r="F15">
-        <v>-2.328554170395363</v>
+        <v>-2.028294181167821</v>
       </c>
       <c r="G15">
-        <v>-1.067124331422645</v>
+        <v>-1.295651569373292</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.79570411406984</v>
       </c>
       <c r="E16">
-        <v>-18.9797378091816</v>
+        <v>-16.95254377727792</v>
       </c>
       <c r="F16">
-        <v>-2.336620812163825</v>
+        <v>-1.893580932287551</v>
       </c>
       <c r="G16">
-        <v>-0.7633029023474214</v>
+        <v>0.5620579536081666</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.303902704892969</v>
       </c>
       <c r="E17">
-        <v>-19.62590123686207</v>
+        <v>-17.48317677607471</v>
       </c>
       <c r="F17">
-        <v>-2.166588462330392</v>
+        <v>-1.365124776039009</v>
       </c>
       <c r="G17">
-        <v>0.09828681717469101</v>
+        <v>1.225160018556349</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.932385561330608</v>
       </c>
       <c r="E18">
-        <v>-20.33315377890602</v>
+        <v>-18.82790260417842</v>
       </c>
       <c r="F18">
-        <v>-2.0394729992686</v>
+        <v>-1.146634589876611</v>
       </c>
       <c r="G18">
-        <v>-0.1221128349732105</v>
+        <v>0.3967303241139851</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.69148082622106</v>
       </c>
       <c r="E19">
-        <v>-21.23035769167571</v>
+        <v>-19.56626123418105</v>
       </c>
       <c r="F19">
-        <v>-1.696667231865872</v>
+        <v>-1.090960016734457</v>
       </c>
       <c r="G19">
-        <v>0.5365464559834839</v>
+        <v>1.084244677464436</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.575600411411988</v>
       </c>
       <c r="E20">
-        <v>-21.9329096776997</v>
+        <v>-19.99887088460781</v>
       </c>
       <c r="F20">
-        <v>-1.244967599160732</v>
+        <v>-0.7429694977576067</v>
       </c>
       <c r="G20">
-        <v>1.092710229087804</v>
+        <v>1.469591337405624</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.577424101993676</v>
       </c>
       <c r="E21">
-        <v>-23.53147458782936</v>
+        <v>-20.79396676545255</v>
       </c>
       <c r="F21">
-        <v>-1.183678351762403</v>
+        <v>-0.54779039867739</v>
       </c>
       <c r="G21">
-        <v>0.8178324553884416</v>
+        <v>0.9871992686222995</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.681023122359877</v>
       </c>
       <c r="E22">
-        <v>-23.50385542485657</v>
+        <v>-21.89761022280991</v>
       </c>
       <c r="F22">
-        <v>-0.8253001055544468</v>
+        <v>-0.114808555805908</v>
       </c>
       <c r="G22">
-        <v>0.2777302618176036</v>
+        <v>1.031046232321159</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.867497702206008</v>
       </c>
       <c r="E23">
-        <v>-24.19209743301632</v>
+        <v>-22.54056296241895</v>
       </c>
       <c r="F23">
-        <v>-0.6738704024856832</v>
+        <v>0.09122215625098221</v>
       </c>
       <c r="G23">
-        <v>0.6051928922286268</v>
+        <v>1.639591426400455</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.114833425197212</v>
       </c>
       <c r="E24">
-        <v>-23.7727924392241</v>
+        <v>-22.97004796578041</v>
       </c>
       <c r="F24">
-        <v>-0.5428003134429258</v>
+        <v>0.2805455261608092</v>
       </c>
       <c r="G24">
-        <v>0.386532287507231</v>
+        <v>0.7056999898159779</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.396653153221131</v>
       </c>
       <c r="E25">
-        <v>-24.80592755628203</v>
+        <v>-22.51726849212349</v>
       </c>
       <c r="F25">
-        <v>-0.2427432742290693</v>
+        <v>0.3289561455478151</v>
       </c>
       <c r="G25">
-        <v>0.06366992972254926</v>
+        <v>0.6067744410202791</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.68903503870742</v>
       </c>
       <c r="E26">
-        <v>-24.69428708657093</v>
+        <v>-23.36737627521341</v>
       </c>
       <c r="F26">
-        <v>-0.5260979415002793</v>
+        <v>0.3462002697718924</v>
       </c>
       <c r="G26">
-        <v>-0.6623856520651397</v>
+        <v>1.222062545404233</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.965424195037452</v>
       </c>
       <c r="E27">
-        <v>-24.68385801093127</v>
+        <v>-23.11092426368502</v>
       </c>
       <c r="F27">
-        <v>-0.5504668537558353</v>
+        <v>0.1952841544928645</v>
       </c>
       <c r="G27">
-        <v>-0.7038504489118426</v>
+        <v>-0.07858086854405751</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.202784761475105</v>
       </c>
       <c r="E28">
-        <v>-24.63043107458878</v>
+        <v>-24.66947557748291</v>
       </c>
       <c r="F28">
-        <v>-0.2726730168596182</v>
+        <v>0.5674456059160012</v>
       </c>
       <c r="G28">
-        <v>-1.252933345890881</v>
+        <v>-0.1512107077623663</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.37991826431228</v>
       </c>
       <c r="E29">
-        <v>-25.06974739502089</v>
+        <v>-23.02576178149678</v>
       </c>
       <c r="F29">
-        <v>-0.3369974024218054</v>
+        <v>0.4247676044578144</v>
       </c>
       <c r="G29">
-        <v>-1.615839731587026</v>
+        <v>-1.161439763927324</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.481430966518479</v>
       </c>
       <c r="E30">
-        <v>-24.63752266488479</v>
+        <v>-22.3595824987024</v>
       </c>
       <c r="F30">
-        <v>-0.1220062401688329</v>
+        <v>0.5439572482096212</v>
       </c>
       <c r="G30">
-        <v>-1.807709162275555</v>
+        <v>-1.206264531650898</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.498305421315896</v>
       </c>
       <c r="E31">
-        <v>-24.81076849499623</v>
+        <v>-22.54715642057411</v>
       </c>
       <c r="F31">
-        <v>-0.2834053449302886</v>
+        <v>0.1781518598681651</v>
       </c>
       <c r="G31">
-        <v>-1.950616204854051</v>
+        <v>-0.540875455275783</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.428159732087296</v>
       </c>
       <c r="E32">
-        <v>-24.55409911671548</v>
+        <v>-22.47696960192923</v>
       </c>
       <c r="F32">
-        <v>-0.216326637753793</v>
+        <v>0.6430854902004296</v>
       </c>
       <c r="G32">
-        <v>-2.136763185142909</v>
+        <v>-1.461087479178935</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.276375595491199</v>
       </c>
       <c r="E33">
-        <v>-24.08513487695515</v>
+        <v>-21.9438323570062</v>
       </c>
       <c r="F33">
-        <v>-0.6980951788131519</v>
+        <v>0.9481848017951268</v>
       </c>
       <c r="G33">
-        <v>-2.243803194855115</v>
+        <v>-2.311389796536557</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.054776477564543</v>
       </c>
       <c r="E34">
-        <v>-24.12936448258807</v>
+        <v>-20.85186783411462</v>
       </c>
       <c r="F34">
-        <v>-0.3422045199158031</v>
+        <v>0.6020697066182149</v>
       </c>
       <c r="G34">
-        <v>-2.770767377301936</v>
+        <v>-2.098320393352455</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.781270698273167</v>
       </c>
       <c r="E35">
-        <v>-22.69758779863491</v>
+        <v>-21.2376711771981</v>
       </c>
       <c r="F35">
-        <v>-0.3388189823405615</v>
+        <v>0.1040502538507354</v>
       </c>
       <c r="G35">
-        <v>-2.846448752570529</v>
+        <v>-3.038049123091184</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.477939053194349</v>
       </c>
       <c r="E36">
-        <v>-22.12144816453505</v>
+        <v>-21.07541595350327</v>
       </c>
       <c r="F36">
-        <v>-0.1398964909670939</v>
+        <v>0.7991830435839685</v>
       </c>
       <c r="G36">
-        <v>-2.344303729999347</v>
+        <v>-1.923437846677171</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.168065809821206</v>
       </c>
       <c r="E37">
-        <v>-21.75823284980183</v>
+        <v>-20.57458484215096</v>
       </c>
       <c r="F37">
-        <v>-0.4203104539583657</v>
+        <v>0.8373326759524969</v>
       </c>
       <c r="G37">
-        <v>-2.98435849471399</v>
+        <v>-2.361727016479998</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.877287852014223</v>
       </c>
       <c r="E38">
-        <v>-21.84696829798213</v>
+        <v>-19.7006029440926</v>
       </c>
       <c r="F38">
-        <v>0.05080528230099152</v>
+        <v>0.7213794636434278</v>
       </c>
       <c r="G38">
-        <v>-2.872688681381408</v>
+        <v>-2.48971106340614</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.628009911132918</v>
       </c>
       <c r="E39">
-        <v>-21.01505139498102</v>
+        <v>-19.569770801537</v>
       </c>
       <c r="F39">
-        <v>-0.3942102538309589</v>
+        <v>1.251436854081581</v>
       </c>
       <c r="G39">
-        <v>-2.340359701684894</v>
+        <v>-2.447435804834254</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.441962305042789</v>
       </c>
       <c r="E40">
-        <v>-20.99122709322667</v>
+        <v>-18.99625768236158</v>
       </c>
       <c r="F40">
-        <v>-0.1644095391507368</v>
+        <v>0.6804680543539657</v>
       </c>
       <c r="G40">
-        <v>-1.931270122539565</v>
+        <v>-2.567896010724589</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.335214747556197</v>
       </c>
       <c r="E41">
-        <v>-19.68434572240507</v>
+        <v>-17.29476961498559</v>
       </c>
       <c r="F41">
-        <v>-0.04142680106151102</v>
+        <v>0.7559273545445839</v>
       </c>
       <c r="G41">
-        <v>-1.95830738818939</v>
+        <v>-2.493451655983907</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.319278145621629</v>
       </c>
       <c r="E42">
-        <v>-20.60899218766124</v>
+        <v>-17.63541501526457</v>
       </c>
       <c r="F42">
-        <v>-0.04900470606232091</v>
+        <v>0.9672455357335433</v>
       </c>
       <c r="G42">
-        <v>-2.272523727164935</v>
+        <v>-2.400747303264915</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.398434795255932</v>
       </c>
       <c r="E43">
-        <v>-19.08893743140256</v>
+        <v>-17.42072459103493</v>
       </c>
       <c r="F43">
-        <v>-0.03974770033603643</v>
+        <v>0.6861945582095187</v>
       </c>
       <c r="G43">
-        <v>-1.805891365531623</v>
+        <v>-2.519317525537009</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.568897143832648</v>
       </c>
       <c r="E44">
-        <v>-19.03949102371281</v>
+        <v>-16.82142181238583</v>
       </c>
       <c r="F44">
-        <v>0.03280237353594987</v>
+        <v>0.573693152867915</v>
       </c>
       <c r="G44">
-        <v>-1.860221832112909</v>
+        <v>-1.48764568648108</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.821938697212891</v>
       </c>
       <c r="E45">
-        <v>-18.70004114057184</v>
+        <v>-16.1692672135932</v>
       </c>
       <c r="F45">
-        <v>-0.1690326576257609</v>
+        <v>0.9191588080010321</v>
       </c>
       <c r="G45">
-        <v>-2.148513239547281</v>
+        <v>-1.366716265907745</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.14014041045687</v>
       </c>
       <c r="E46">
-        <v>-18.13524080538718</v>
+        <v>-15.20543586274866</v>
       </c>
       <c r="F46">
-        <v>0.1889794501901575</v>
+        <v>0.8692165372862499</v>
       </c>
       <c r="G46">
-        <v>-1.64843210533699</v>
+        <v>-1.056417705474177</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.505995778064088</v>
       </c>
       <c r="E47">
-        <v>-18.21084820741925</v>
+        <v>-14.47674099627839</v>
       </c>
       <c r="F47">
-        <v>0.07673069690640766</v>
+        <v>1.002300387485213</v>
       </c>
       <c r="G47">
-        <v>-1.606685123436175</v>
+        <v>-1.896869795710347</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.896460524319008</v>
       </c>
       <c r="E48">
-        <v>-16.43179190876587</v>
+        <v>-14.88829324256948</v>
       </c>
       <c r="F48">
-        <v>0.02602135797663312</v>
+        <v>0.6826557726647592</v>
       </c>
       <c r="G48">
-        <v>-2.513624606131373</v>
+        <v>-1.782256726638943</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.291622105955805</v>
       </c>
       <c r="E49">
-        <v>-17.47246240657256</v>
+        <v>-15.25195687622946</v>
       </c>
       <c r="F49">
-        <v>-0.01175053885621874</v>
+        <v>0.7709555959661726</v>
       </c>
       <c r="G49">
-        <v>-1.917971331559136</v>
+        <v>-0.3682307017040398</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.673109843549585</v>
       </c>
       <c r="E50">
-        <v>-16.47280176937933</v>
+        <v>-13.60973294819185</v>
       </c>
       <c r="F50">
-        <v>0.04977562161931174</v>
+        <v>0.671604523144011</v>
       </c>
       <c r="G50">
-        <v>-1.986217458774026</v>
+        <v>-1.045074522543177</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.025703111648141</v>
       </c>
       <c r="E51">
-        <v>-16.15685466633818</v>
+        <v>-12.58346752620355</v>
       </c>
       <c r="F51">
-        <v>0.2269103935643468</v>
+        <v>0.9289136625363991</v>
       </c>
       <c r="G51">
-        <v>-2.359312037412247</v>
+        <v>-1.311033936043968</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.342759410329931</v>
       </c>
       <c r="E52">
-        <v>-15.73103772692293</v>
+        <v>-13.58888838233454</v>
       </c>
       <c r="F52">
-        <v>0.2465410442758895</v>
+        <v>0.6792255032497665</v>
       </c>
       <c r="G52">
-        <v>-1.970516813612083</v>
+        <v>-0.499476282860269</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.617987218906997</v>
       </c>
       <c r="E53">
-        <v>-13.90714953559361</v>
+        <v>-13.60526787282028</v>
       </c>
       <c r="F53">
-        <v>-0.1307281205529089</v>
+        <v>0.4362330376799623</v>
       </c>
       <c r="G53">
-        <v>-2.468173125089944</v>
+        <v>-1.769368088353444</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.854927626977027</v>
       </c>
       <c r="E54">
-        <v>-14.2147914173047</v>
+        <v>-12.31502864397687</v>
       </c>
       <c r="F54">
-        <v>0.03700550973775456</v>
+        <v>0.8634908617980998</v>
       </c>
       <c r="G54">
-        <v>-2.340723917277993</v>
+        <v>-2.087469393655371</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.056688711117959</v>
       </c>
       <c r="E55">
-        <v>-15.57473291807418</v>
+        <v>-12.36904881041437</v>
       </c>
       <c r="F55">
-        <v>0.117297505356305</v>
+        <v>0.9797340026981487</v>
       </c>
       <c r="G55">
-        <v>-2.491207300437246</v>
+        <v>-1.870465805821495</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.229268517628587</v>
       </c>
       <c r="E56">
-        <v>-13.45456025784502</v>
+        <v>-10.85729474701175</v>
       </c>
       <c r="F56">
-        <v>0.1021060755563649</v>
+        <v>1.017234195022882</v>
       </c>
       <c r="G56">
-        <v>-2.73712501265295</v>
+        <v>-1.936287110303956</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.378575181805243</v>
       </c>
       <c r="E57">
-        <v>-13.38802338925032</v>
+        <v>-11.15943453280352</v>
       </c>
       <c r="F57">
-        <v>0.3608458054533877</v>
+        <v>0.6774759912950539</v>
       </c>
       <c r="G57">
-        <v>-3.196184314927062</v>
+        <v>-2.290859193239112</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.505952064030533</v>
       </c>
       <c r="E58">
-        <v>-12.77340078303326</v>
+        <v>-10.52693351120418</v>
       </c>
       <c r="F58">
-        <v>0.465593691904788</v>
+        <v>1.048861262461767</v>
       </c>
       <c r="G58">
-        <v>-3.146132561259293</v>
+        <v>-3.122999949265207</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.616463701607866</v>
       </c>
       <c r="E59">
-        <v>-12.38360332587502</v>
+        <v>-10.61695504600266</v>
       </c>
       <c r="F59">
-        <v>0.2713597600311655</v>
+        <v>0.9781750152460801</v>
       </c>
       <c r="G59">
-        <v>-3.213919317455861</v>
+        <v>-3.079405639626425</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.710579990430083</v>
       </c>
       <c r="E60">
-        <v>-13.09162118002627</v>
+        <v>-9.226251621299081</v>
       </c>
       <c r="F60">
-        <v>0.2661700382526266</v>
+        <v>1.054194291800991</v>
       </c>
       <c r="G60">
-        <v>-3.689745661898737</v>
+        <v>-3.572320585950889</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.789319120989598</v>
       </c>
       <c r="E61">
-        <v>-12.15134695096963</v>
+        <v>-9.481856808188027</v>
       </c>
       <c r="F61">
-        <v>0.5192901236890575</v>
+        <v>1.020034076844345</v>
       </c>
       <c r="G61">
-        <v>-3.28258872225192</v>
+        <v>-2.615979031456691</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.853639193781069</v>
       </c>
       <c r="E62">
-        <v>-11.41228187902179</v>
+        <v>-8.807693825718125</v>
       </c>
       <c r="F62">
-        <v>0.3848651466649621</v>
+        <v>1.134371972717955</v>
       </c>
       <c r="G62">
-        <v>-4.948353346448982</v>
+        <v>-2.98157930005314</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.901467654344703</v>
       </c>
       <c r="E63">
-        <v>-11.4219682849242</v>
+        <v>-8.589765542572996</v>
       </c>
       <c r="F63">
-        <v>0.262127605326965</v>
+        <v>0.918671727968186</v>
       </c>
       <c r="G63">
-        <v>-4.179103764052762</v>
+        <v>-4.032885968920787</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.932296701786369</v>
       </c>
       <c r="E64">
-        <v>-11.46632015935532</v>
+        <v>-8.399365852920496</v>
       </c>
       <c r="F64">
-        <v>0.1867759928987108</v>
+        <v>0.4299092809269909</v>
       </c>
       <c r="G64">
-        <v>-4.346574031225261</v>
+        <v>-4.742417318935112</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.942100765860724</v>
       </c>
       <c r="E65">
-        <v>-11.37823681143213</v>
+        <v>-9.111169511342155</v>
       </c>
       <c r="F65">
-        <v>0.3140960627089948</v>
+        <v>0.9561222182487517</v>
       </c>
       <c r="G65">
-        <v>-4.441283210317073</v>
+        <v>-5.006558935691971</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.928493813757439</v>
       </c>
       <c r="E66">
-        <v>-10.90149265332662</v>
+        <v>-9.887780161287582</v>
       </c>
       <c r="F66">
-        <v>0.004521910404374749</v>
+        <v>0.6274061520002406</v>
       </c>
       <c r="G66">
-        <v>-4.281366315174416</v>
+        <v>-3.796129427299053</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.892316620831003</v>
       </c>
       <c r="E67">
-        <v>-11.23882321063199</v>
+        <v>-8.533069047996964</v>
       </c>
       <c r="F67">
-        <v>0.07859203846049814</v>
+        <v>0.7742939165994546</v>
       </c>
       <c r="G67">
-        <v>-4.502481273622276</v>
+        <v>-4.60043558083638</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.835137248983815</v>
       </c>
       <c r="E68">
-        <v>-10.313696727131</v>
+        <v>-8.776850389251882</v>
       </c>
       <c r="F68">
-        <v>0.09087424194180642</v>
+        <v>0.6429595783552041</v>
       </c>
       <c r="G68">
-        <v>-4.954006891195904</v>
+        <v>-4.280083357544673</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.764552005737886</v>
       </c>
       <c r="E69">
-        <v>-10.0664420463122</v>
+        <v>-8.029951057270779</v>
       </c>
       <c r="F69">
-        <v>-0.04235457255264648</v>
+        <v>0.6521130381561386</v>
       </c>
       <c r="G69">
-        <v>-5.509068173856251</v>
+        <v>-4.036387032324714</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.686884096331964</v>
       </c>
       <c r="E70">
-        <v>-10.41719952905032</v>
+        <v>-8.860599987549739</v>
       </c>
       <c r="F70">
-        <v>-0.08946962532167395</v>
+        <v>0.4542367748124068</v>
       </c>
       <c r="G70">
-        <v>-5.201913023676631</v>
+        <v>-3.769246379062523</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.612300499067239</v>
       </c>
       <c r="E71">
-        <v>-10.68010008756562</v>
+        <v>-7.050922147656494</v>
       </c>
       <c r="F71">
-        <v>-0.2447454382416357</v>
+        <v>0.1443668953449873</v>
       </c>
       <c r="G71">
-        <v>-4.611214393659155</v>
+        <v>-4.436879810984299</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.549629350763047</v>
       </c>
       <c r="E72">
-        <v>-10.98550490311692</v>
+        <v>-8.538399061903991</v>
       </c>
       <c r="F72">
-        <v>-0.3562528026998799</v>
+        <v>0.4769274147098908</v>
       </c>
       <c r="G72">
-        <v>-4.948159754376974</v>
+        <v>-4.137051628546919</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.504907892996703</v>
       </c>
       <c r="E73">
-        <v>-10.60705127334789</v>
+        <v>-7.913220582775061</v>
       </c>
       <c r="F73">
-        <v>-0.6131311910428122</v>
+        <v>0.4800122549179162</v>
       </c>
       <c r="G73">
-        <v>-4.72322545403392</v>
+        <v>-5.071838838617124</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.484458171204402</v>
       </c>
       <c r="E74">
-        <v>-10.73407496926304</v>
+        <v>-9.476889072201612</v>
       </c>
       <c r="F74">
-        <v>-0.4245699191435607</v>
+        <v>0.05930350348631165</v>
       </c>
       <c r="G74">
-        <v>-5.307171330082058</v>
+        <v>-4.306411879337658</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.488201355359644</v>
       </c>
       <c r="E75">
-        <v>-11.25664275585217</v>
+        <v>-8.914583926195176</v>
       </c>
       <c r="F75">
-        <v>-0.5744572021083117</v>
+        <v>0.5287359971831803</v>
       </c>
       <c r="G75">
-        <v>-4.546374174422969</v>
+        <v>-3.827428999754596</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.514849508855712</v>
       </c>
       <c r="E76">
-        <v>-11.69191062052143</v>
+        <v>-9.243541335060366</v>
       </c>
       <c r="F76">
-        <v>-0.5153639566948034</v>
+        <v>0.08815968196283243</v>
       </c>
       <c r="G76">
-        <v>-4.40720772442224</v>
+        <v>-3.915191832805064</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.558182965221767</v>
       </c>
       <c r="E77">
-        <v>-11.73407071353284</v>
+        <v>-9.072211049454166</v>
       </c>
       <c r="F77">
-        <v>-0.7647157988158994</v>
+        <v>0.06364580541178666</v>
       </c>
       <c r="G77">
-        <v>-4.498835836469733</v>
+        <v>-3.393490729739592</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.608954130512796</v>
       </c>
       <c r="E78">
-        <v>-12.12508180172514</v>
+        <v>-9.430132578072415</v>
       </c>
       <c r="F78">
-        <v>-0.6111605049915522</v>
+        <v>-0.01959269305852166</v>
       </c>
       <c r="G78">
-        <v>-4.203998392024269</v>
+        <v>-2.681583775316229</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.658648468498177</v>
       </c>
       <c r="E79">
-        <v>-12.14527426732534</v>
+        <v>-10.61822754719882</v>
       </c>
       <c r="F79">
-        <v>-0.5301776509590669</v>
+        <v>0.4479999966367293</v>
       </c>
       <c r="G79">
-        <v>-4.11801726228058</v>
+        <v>-3.624718413033661</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.693978442097614</v>
       </c>
       <c r="E80">
-        <v>-12.74313699124</v>
+        <v>-10.80787098169204</v>
       </c>
       <c r="F80">
-        <v>-0.515365613429609</v>
+        <v>-0.1697831584926972</v>
       </c>
       <c r="G80">
-        <v>-3.277985168404019</v>
+        <v>-3.052886806982993</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.704005657006694</v>
       </c>
       <c r="E81">
-        <v>-12.79232980438533</v>
+        <v>-12.12461536890235</v>
       </c>
       <c r="F81">
-        <v>-0.7794441712376745</v>
+        <v>-0.4556784285882934</v>
       </c>
       <c r="G81">
-        <v>-3.54660893381108</v>
+        <v>-2.946017420791879</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.676959776210314</v>
       </c>
       <c r="E82">
-        <v>-14.02726730864707</v>
+        <v>-12.12137750998686</v>
       </c>
       <c r="F82">
-        <v>-0.9290423539788485</v>
+        <v>-0.1264554014892691</v>
       </c>
       <c r="G82">
-        <v>-3.495749999639687</v>
+        <v>-3.110478807794367</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.604445880747631</v>
       </c>
       <c r="E83">
-        <v>-15.09228741119301</v>
+        <v>-12.39630116699253</v>
       </c>
       <c r="F83">
-        <v>-1.00360618900704</v>
+        <v>-0.08254116036465889</v>
       </c>
       <c r="G83">
-        <v>-3.663279328800256</v>
+        <v>-2.596885603202282</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.482455579217676</v>
       </c>
       <c r="E84">
-        <v>-15.87901920054558</v>
+        <v>-13.63748343691085</v>
       </c>
       <c r="F84">
-        <v>-1.310395370103449</v>
+        <v>-0.228787768594106</v>
       </c>
       <c r="G84">
-        <v>-3.76512844600542</v>
+        <v>-1.385872037371783</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.306721643107766</v>
       </c>
       <c r="E85">
-        <v>-17.48258354597971</v>
+        <v>-15.07867481832595</v>
       </c>
       <c r="F85">
-        <v>-1.049387570257561</v>
+        <v>-0.4924720235184391</v>
       </c>
       <c r="G85">
-        <v>-3.612029929263289</v>
+        <v>-3.049638397639143</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.080476487247515</v>
       </c>
       <c r="E86">
-        <v>-17.81976013516882</v>
+        <v>-17.03249851435735</v>
       </c>
       <c r="F86">
-        <v>-0.9660115627983876</v>
+        <v>-1.060820697150999</v>
       </c>
       <c r="G86">
-        <v>-3.160783215522213</v>
+        <v>-1.753286821490605</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.808834451823948</v>
       </c>
       <c r="E87">
-        <v>-19.0317518616337</v>
+        <v>-17.64675884265379</v>
       </c>
       <c r="F87">
-        <v>-1.133194328766189</v>
+        <v>-0.2523539928363491</v>
       </c>
       <c r="G87">
-        <v>-3.154230616068002</v>
+        <v>-2.223226654455837</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.505431513135905</v>
       </c>
       <c r="E88">
-        <v>-20.55562412148084</v>
+        <v>-19.67599068786091</v>
       </c>
       <c r="F88">
-        <v>-1.284615748160925</v>
+        <v>-0.1999440156286272</v>
       </c>
       <c r="G88">
-        <v>-2.892448197612384</v>
+        <v>-2.12948871694562</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.189658620823487</v>
       </c>
       <c r="E89">
-        <v>-21.99775289701553</v>
+        <v>-20.2851428974767</v>
       </c>
       <c r="F89">
-        <v>-1.278890072672775</v>
+        <v>-0.4555210387817615</v>
       </c>
       <c r="G89">
-        <v>-2.556346110835343</v>
+        <v>-1.56842279883149</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.885241087683025</v>
       </c>
       <c r="E90">
-        <v>-22.82448016880385</v>
+        <v>-20.97709372584873</v>
       </c>
       <c r="F90">
-        <v>-1.313827296253247</v>
+        <v>-0.8523595551342954</v>
       </c>
       <c r="G90">
-        <v>-2.911479282657163</v>
+        <v>-1.852556898550046</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.621726057196947</v>
       </c>
       <c r="E91">
-        <v>-24.69923670866132</v>
+        <v>-23.24756643839247</v>
       </c>
       <c r="F91">
-        <v>-1.524997199677105</v>
+        <v>-1.320736708759997</v>
       </c>
       <c r="G91">
-        <v>-2.930979582384943</v>
+        <v>-2.210393796936849</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.426219058419371</v>
       </c>
       <c r="E92">
-        <v>-26.7924966478629</v>
+        <v>-24.87324785088006</v>
       </c>
       <c r="F92">
-        <v>-1.626652790613855</v>
+        <v>-1.374285691146569</v>
       </c>
       <c r="G92">
-        <v>-2.543910281125048</v>
+        <v>-2.404776643339913</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.329204683738288</v>
       </c>
       <c r="E93">
-        <v>-28.95589359249527</v>
+        <v>-26.71289060328206</v>
       </c>
       <c r="F93">
-        <v>-1.710935860379093</v>
+        <v>-1.079579905354797</v>
       </c>
       <c r="G93">
-        <v>-2.630856090007213</v>
+        <v>-1.632406619240662</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.352731118024335</v>
       </c>
       <c r="E94">
-        <v>-30.99038526026231</v>
+        <v>-28.98733931600453</v>
       </c>
       <c r="F94">
-        <v>-2.091169752142511</v>
+        <v>-1.451747155349753</v>
       </c>
       <c r="G94">
-        <v>-2.928571165760311</v>
+        <v>-2.214846414593015</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.515528856132652</v>
       </c>
       <c r="E95">
-        <v>-32.67329752725883</v>
+        <v>-32.23036522033159</v>
       </c>
       <c r="F95">
-        <v>-1.9427735305028</v>
+        <v>-1.4070211141704</v>
       </c>
       <c r="G95">
-        <v>-3.374676205317736</v>
+        <v>-2.944951023785059</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.833345121357028</v>
       </c>
       <c r="E96">
-        <v>-35.59040689301685</v>
+        <v>-34.29407686663312</v>
       </c>
       <c r="F96">
-        <v>-2.087320328821702</v>
+        <v>-1.719966721804414</v>
       </c>
       <c r="G96">
-        <v>-3.321832132102879</v>
+        <v>-2.172630218009199</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.292429427202888</v>
       </c>
       <c r="E97">
-        <v>-37.35330106793685</v>
+        <v>-36.27509178484357</v>
       </c>
       <c r="F97">
-        <v>-2.584653065012261</v>
+        <v>-2.06747098911582</v>
       </c>
       <c r="G97">
-        <v>-3.737789307972126</v>
+        <v>-2.52203109576667</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.904048672070689</v>
       </c>
       <c r="E98">
-        <v>-40.18251728168</v>
+        <v>-39.36845615169113</v>
       </c>
       <c r="F98">
-        <v>-2.302559172928111</v>
+        <v>-1.85007176282291</v>
       </c>
       <c r="G98">
-        <v>-3.623215613559436</v>
+        <v>-3.586177184596424</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.610919231213673</v>
       </c>
       <c r="E99">
-        <v>-42.7691793706243</v>
+        <v>-42.03280421223702</v>
       </c>
       <c r="F99">
-        <v>-2.449355817113017</v>
+        <v>-2.216710488771582</v>
       </c>
       <c r="G99">
-        <v>-3.798550968809923</v>
+        <v>-3.232166190547933</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.443011287586641</v>
       </c>
       <c r="E100">
-        <v>-44.29429696082355</v>
+        <v>-44.06352818962968</v>
       </c>
       <c r="F100">
-        <v>-3.068302000075974</v>
+        <v>-2.656268740453889</v>
       </c>
       <c r="G100">
-        <v>-4.908939313076932</v>
+        <v>-3.692446107242159</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.281893100113844</v>
       </c>
       <c r="E101">
-        <v>-46.86171077099826</v>
+        <v>-46.28786480898327</v>
       </c>
       <c r="F101">
-        <v>-2.939330994031911</v>
+        <v>-2.561070273421961</v>
       </c>
       <c r="G101">
-        <v>-5.281069212576676</v>
+        <v>-4.660737870655855</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.247280800461825</v>
       </c>
       <c r="E102">
-        <v>-49.81018095137789</v>
+        <v>-47.76286577733963</v>
       </c>
       <c r="F102">
-        <v>-3.334099420244849</v>
+        <v>-2.336393011128055</v>
       </c>
       <c r="G102">
-        <v>-5.029009053601691</v>
+        <v>-4.617471683173017</v>
       </c>
     </row>
   </sheetData>
